--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C662"/>
+  <dimension ref="A1:C663"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6791,881 +6791,892 @@
     </row>
     <row r="583" spans="1:3">
       <c r="A583" s="2">
-        <v>46082</v>
+        <v>46062</v>
       </c>
       <c r="B583">
         <v>1</v>
       </c>
       <c r="C583">
-        <v>505.53</v>
+        <v>458.45</v>
       </c>
     </row>
     <row r="584" spans="1:3">
       <c r="A584" s="2">
-        <v>46083</v>
+        <v>46082</v>
       </c>
       <c r="B584">
         <v>1</v>
       </c>
       <c r="C584">
-        <v>505.17</v>
+        <v>505.53</v>
       </c>
     </row>
     <row r="585" spans="1:3">
       <c r="A585" s="2">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="B585">
         <v>1</v>
       </c>
       <c r="C585">
-        <v>502.6</v>
+        <v>505.17</v>
       </c>
     </row>
     <row r="586" spans="1:3">
       <c r="A586" s="2">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="B586">
         <v>1</v>
       </c>
       <c r="C586">
-        <v>472.31</v>
+        <v>502.6</v>
       </c>
     </row>
     <row r="587" spans="1:3">
       <c r="A587" s="2">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="B587">
         <v>1</v>
       </c>
       <c r="C587">
-        <v>462.91</v>
+        <v>472.31</v>
       </c>
     </row>
     <row r="588" spans="1:3">
       <c r="A588" s="2">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="B588">
         <v>1</v>
       </c>
       <c r="C588">
-        <v>493.15</v>
+        <v>462.91</v>
       </c>
     </row>
     <row r="589" spans="1:3">
       <c r="A589" s="2">
-        <v>46088</v>
+        <v>46087</v>
       </c>
       <c r="B589">
         <v>1</v>
       </c>
       <c r="C589">
-        <v>474.47</v>
+        <v>493.15</v>
       </c>
     </row>
     <row r="590" spans="1:3">
       <c r="A590" s="2">
-        <v>46089</v>
+        <v>46088</v>
       </c>
       <c r="B590">
         <v>1</v>
       </c>
       <c r="C590">
-        <v>473.59</v>
+        <v>474.47</v>
       </c>
     </row>
     <row r="591" spans="1:3">
       <c r="A591" s="2">
-        <v>46113</v>
+        <v>46089</v>
       </c>
       <c r="B591">
         <v>1</v>
       </c>
       <c r="C591">
-        <v>505.53</v>
+        <v>473.59</v>
       </c>
     </row>
     <row r="592" spans="1:3">
       <c r="A592" s="2">
-        <v>46114</v>
+        <v>46113</v>
       </c>
       <c r="B592">
         <v>1</v>
       </c>
       <c r="C592">
-        <v>503.44</v>
+        <v>505.53</v>
       </c>
     </row>
     <row r="593" spans="1:3">
       <c r="A593" s="2">
-        <v>46115</v>
+        <v>46114</v>
       </c>
       <c r="B593">
         <v>1</v>
       </c>
       <c r="C593">
-        <v>498.09</v>
+        <v>503.44</v>
       </c>
     </row>
     <row r="594" spans="1:3">
       <c r="A594" s="2">
-        <v>46116</v>
+        <v>46115</v>
       </c>
       <c r="B594">
         <v>1</v>
       </c>
       <c r="C594">
-        <v>470.46</v>
+        <v>498.09</v>
       </c>
     </row>
     <row r="595" spans="1:3">
       <c r="A595" s="2">
-        <v>46117</v>
+        <v>46116</v>
       </c>
       <c r="B595">
         <v>1</v>
       </c>
       <c r="C595">
-        <v>462.91</v>
+        <v>470.46</v>
       </c>
     </row>
     <row r="596" spans="1:3">
       <c r="A596" s="2">
-        <v>46118</v>
+        <v>46117</v>
       </c>
       <c r="B596">
         <v>1</v>
       </c>
       <c r="C596">
-        <v>489.31</v>
+        <v>462.91</v>
       </c>
     </row>
     <row r="597" spans="1:3">
       <c r="A597" s="2">
-        <v>46119</v>
+        <v>46118</v>
       </c>
       <c r="B597">
         <v>1</v>
       </c>
       <c r="C597">
-        <v>472.03</v>
+        <v>489.31</v>
       </c>
     </row>
     <row r="598" spans="1:3">
       <c r="A598" s="2">
-        <v>46120</v>
+        <v>46119</v>
       </c>
       <c r="B598">
         <v>1</v>
       </c>
       <c r="C598">
-        <v>475.38</v>
+        <v>472.03</v>
       </c>
     </row>
     <row r="599" spans="1:3">
       <c r="A599" s="2">
-        <v>46143</v>
+        <v>46120</v>
       </c>
       <c r="B599">
         <v>1</v>
       </c>
       <c r="C599">
-        <v>505.53</v>
+        <v>475.38</v>
       </c>
     </row>
     <row r="600" spans="1:3">
       <c r="A600" s="2">
-        <v>46144</v>
+        <v>46143</v>
       </c>
       <c r="B600">
         <v>1</v>
       </c>
       <c r="C600">
-        <v>498.65</v>
+        <v>505.53</v>
       </c>
     </row>
     <row r="601" spans="1:3">
       <c r="A601" s="2">
-        <v>46145</v>
+        <v>46144</v>
       </c>
       <c r="B601">
         <v>1</v>
       </c>
       <c r="C601">
-        <v>499.83</v>
+        <v>498.65</v>
       </c>
     </row>
     <row r="602" spans="1:3">
       <c r="A602" s="2">
-        <v>46146</v>
+        <v>46145</v>
       </c>
       <c r="B602">
         <v>1</v>
       </c>
       <c r="C602">
-        <v>470.46</v>
+        <v>499.83</v>
       </c>
     </row>
     <row r="603" spans="1:3">
       <c r="A603" s="2">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B603">
         <v>1</v>
       </c>
       <c r="C603">
-        <v>464.53</v>
+        <v>470.46</v>
       </c>
     </row>
     <row r="604" spans="1:3">
       <c r="A604" s="2">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B604">
         <v>1</v>
       </c>
       <c r="C604">
-        <v>485.34</v>
+        <v>464.53</v>
       </c>
     </row>
     <row r="605" spans="1:3">
       <c r="A605" s="2">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="B605">
         <v>1</v>
       </c>
       <c r="C605">
-        <v>472.03</v>
+        <v>485.34</v>
       </c>
     </row>
     <row r="606" spans="1:3">
       <c r="A606" s="2">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="B606">
         <v>1</v>
       </c>
       <c r="C606">
-        <v>471.98</v>
+        <v>472.03</v>
       </c>
     </row>
     <row r="607" spans="1:3">
       <c r="A607" s="2">
-        <v>46174</v>
+        <v>46150</v>
       </c>
       <c r="B607">
         <v>1</v>
       </c>
       <c r="C607">
-        <v>511.26</v>
+        <v>471.98</v>
       </c>
     </row>
     <row r="608" spans="1:3">
       <c r="A608" s="2">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B608">
         <v>1</v>
       </c>
       <c r="C608">
-        <v>495.1</v>
+        <v>511.26</v>
       </c>
     </row>
     <row r="609" spans="1:3">
       <c r="A609" s="2">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="B609">
         <v>1</v>
       </c>
       <c r="C609">
-        <v>493.36</v>
+        <v>495.1</v>
       </c>
     </row>
     <row r="610" spans="1:3">
       <c r="A610" s="2">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="B610">
         <v>1</v>
       </c>
       <c r="C610">
-        <v>470.46</v>
+        <v>493.36</v>
       </c>
     </row>
     <row r="611" spans="1:3">
       <c r="A611" s="2">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="B611">
         <v>1</v>
       </c>
       <c r="C611">
-        <v>465.01</v>
+        <v>470.46</v>
       </c>
     </row>
     <row r="612" spans="1:3">
       <c r="A612" s="2">
-        <v>46179</v>
+        <v>46178</v>
       </c>
       <c r="B612">
         <v>1</v>
       </c>
       <c r="C612">
-        <v>487.44</v>
+        <v>465.01</v>
       </c>
     </row>
     <row r="613" spans="1:3">
       <c r="A613" s="2">
-        <v>46180</v>
+        <v>46179</v>
       </c>
       <c r="B613">
         <v>1</v>
       </c>
       <c r="C613">
-        <v>472.03</v>
+        <v>487.44</v>
       </c>
     </row>
     <row r="614" spans="1:3">
       <c r="A614" s="2">
-        <v>46181</v>
+        <v>46180</v>
       </c>
       <c r="B614">
         <v>1</v>
       </c>
       <c r="C614">
-        <v>469.85</v>
+        <v>472.03</v>
       </c>
     </row>
     <row r="615" spans="1:3">
       <c r="A615" s="2">
-        <v>46204</v>
+        <v>46181</v>
       </c>
       <c r="B615">
         <v>1</v>
       </c>
       <c r="C615">
-        <v>512.83</v>
+        <v>469.85</v>
       </c>
     </row>
     <row r="616" spans="1:3">
       <c r="A616" s="2">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B616">
         <v>1</v>
       </c>
       <c r="C616">
-        <v>494.63</v>
+        <v>512.83</v>
       </c>
     </row>
     <row r="617" spans="1:3">
       <c r="A617" s="2">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="B617">
         <v>1</v>
       </c>
       <c r="C617">
-        <v>493.85</v>
+        <v>494.63</v>
       </c>
     </row>
     <row r="618" spans="1:3">
       <c r="A618" s="2">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="B618">
         <v>1</v>
       </c>
       <c r="C618">
-        <v>466.33</v>
+        <v>493.85</v>
       </c>
     </row>
     <row r="619" spans="1:3">
       <c r="A619" s="2">
-        <v>46208</v>
+        <v>46207</v>
       </c>
       <c r="B619">
         <v>1</v>
       </c>
       <c r="C619">
-        <v>463.41</v>
+        <v>466.33</v>
       </c>
     </row>
     <row r="620" spans="1:3">
       <c r="A620" s="2">
-        <v>46209</v>
+        <v>46208</v>
       </c>
       <c r="B620">
         <v>1</v>
       </c>
       <c r="C620">
-        <v>487.44</v>
+        <v>463.41</v>
       </c>
     </row>
     <row r="621" spans="1:3">
       <c r="A621" s="2">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B621">
         <v>1</v>
       </c>
       <c r="C621">
-        <v>472.03</v>
+        <v>487.44</v>
       </c>
     </row>
     <row r="622" spans="1:3">
       <c r="A622" s="2">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="B622">
         <v>1</v>
       </c>
       <c r="C622">
-        <v>467.48</v>
+        <v>472.03</v>
       </c>
     </row>
     <row r="623" spans="1:3">
       <c r="A623" s="2">
-        <v>46235</v>
+        <v>46211</v>
       </c>
       <c r="B623">
         <v>1</v>
       </c>
       <c r="C623">
-        <v>512.83</v>
+        <v>467.48</v>
       </c>
     </row>
     <row r="624" spans="1:3">
       <c r="A624" s="2">
-        <v>46236</v>
+        <v>46235</v>
       </c>
       <c r="B624">
         <v>1</v>
       </c>
       <c r="C624">
-        <v>494.63</v>
+        <v>512.83</v>
       </c>
     </row>
     <row r="625" spans="1:3">
       <c r="A625" s="2">
-        <v>46237</v>
+        <v>46236</v>
       </c>
       <c r="B625">
         <v>1</v>
       </c>
       <c r="C625">
-        <v>493.85</v>
+        <v>494.63</v>
       </c>
     </row>
     <row r="626" spans="1:3">
       <c r="A626" s="2">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B626">
         <v>1</v>
       </c>
       <c r="C626">
-        <v>460.37</v>
+        <v>493.85</v>
       </c>
     </row>
     <row r="627" spans="1:3">
       <c r="A627" s="2">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B627">
         <v>1</v>
       </c>
       <c r="C627">
-        <v>463.41</v>
+        <v>460.37</v>
       </c>
     </row>
     <row r="628" spans="1:3">
       <c r="A628" s="2">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B628">
         <v>1</v>
       </c>
       <c r="C628">
-        <v>487.44</v>
+        <v>463.41</v>
       </c>
     </row>
     <row r="629" spans="1:3">
       <c r="A629" s="2">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="B629">
         <v>1</v>
       </c>
       <c r="C629">
-        <v>471.04</v>
+        <v>487.44</v>
       </c>
     </row>
     <row r="630" spans="1:3">
       <c r="A630" s="2">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="B630">
         <v>1</v>
       </c>
       <c r="C630">
-        <v>469.93</v>
+        <v>471.04</v>
       </c>
     </row>
     <row r="631" spans="1:3">
       <c r="A631" s="2">
-        <v>46266</v>
+        <v>46242</v>
       </c>
       <c r="B631">
         <v>1</v>
       </c>
       <c r="C631">
-        <v>508.91</v>
+        <v>469.93</v>
       </c>
     </row>
     <row r="632" spans="1:3">
       <c r="A632" s="2">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B632">
         <v>1</v>
       </c>
       <c r="C632">
-        <v>494.63</v>
+        <v>508.91</v>
       </c>
     </row>
     <row r="633" spans="1:3">
       <c r="A633" s="2">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B633">
         <v>1</v>
       </c>
       <c r="C633">
-        <v>493.85</v>
+        <v>494.63</v>
       </c>
     </row>
     <row r="634" spans="1:3">
       <c r="A634" s="2">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B634">
         <v>1</v>
       </c>
       <c r="C634">
-        <v>475.31</v>
+        <v>493.85</v>
       </c>
     </row>
     <row r="635" spans="1:3">
       <c r="A635" s="2">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B635">
         <v>1</v>
       </c>
       <c r="C635">
-        <v>461.26</v>
+        <v>475.31</v>
       </c>
     </row>
     <row r="636" spans="1:3">
       <c r="A636" s="2">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B636">
         <v>1</v>
       </c>
       <c r="C636">
-        <v>484.78</v>
+        <v>461.26</v>
       </c>
     </row>
     <row r="637" spans="1:3">
       <c r="A637" s="2">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B637">
         <v>1</v>
       </c>
       <c r="C637">
-        <v>467.98</v>
+        <v>484.78</v>
       </c>
     </row>
     <row r="638" spans="1:3">
       <c r="A638" s="2">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B638">
         <v>1</v>
       </c>
       <c r="C638">
-        <v>469.93</v>
+        <v>467.98</v>
       </c>
     </row>
     <row r="639" spans="1:3">
       <c r="A639" s="2">
-        <v>46296</v>
+        <v>46273</v>
       </c>
       <c r="B639">
         <v>1</v>
       </c>
       <c r="C639">
-        <v>509.94</v>
+        <v>469.93</v>
       </c>
     </row>
     <row r="640" spans="1:3">
       <c r="A640" s="2">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="B640">
         <v>1</v>
       </c>
       <c r="C640">
-        <v>494.75</v>
+        <v>509.94</v>
       </c>
     </row>
     <row r="641" spans="1:3">
       <c r="A641" s="2">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="B641">
         <v>1</v>
       </c>
       <c r="C641">
-        <v>493.85</v>
+        <v>494.75</v>
       </c>
     </row>
     <row r="642" spans="1:3">
       <c r="A642" s="2">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="B642">
         <v>1</v>
       </c>
       <c r="C642">
-        <v>479.82</v>
+        <v>493.85</v>
       </c>
     </row>
     <row r="643" spans="1:3">
       <c r="A643" s="2">
-        <v>46300</v>
+        <v>46299</v>
       </c>
       <c r="B643">
         <v>1</v>
       </c>
       <c r="C643">
-        <v>461.26</v>
+        <v>479.82</v>
       </c>
     </row>
     <row r="644" spans="1:3">
       <c r="A644" s="2">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="B644">
         <v>1</v>
       </c>
       <c r="C644">
-        <v>490.21</v>
+        <v>461.26</v>
       </c>
     </row>
     <row r="645" spans="1:3">
       <c r="A645" s="2">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="B645">
         <v>1</v>
       </c>
       <c r="C645">
-        <v>467.41</v>
+        <v>490.21</v>
       </c>
     </row>
     <row r="646" spans="1:3">
       <c r="A646" s="2">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="B646">
         <v>1</v>
       </c>
       <c r="C646">
-        <v>469.93</v>
+        <v>467.41</v>
       </c>
     </row>
     <row r="647" spans="1:3">
       <c r="A647" s="2">
-        <v>46327</v>
+        <v>46303</v>
       </c>
       <c r="B647">
         <v>1</v>
       </c>
       <c r="C647">
-        <v>509.94</v>
+        <v>469.93</v>
       </c>
     </row>
     <row r="648" spans="1:3">
       <c r="A648" s="2">
-        <v>46328</v>
+        <v>46327</v>
       </c>
       <c r="B648">
         <v>1</v>
       </c>
       <c r="C648">
-        <v>491.88</v>
+        <v>509.94</v>
       </c>
     </row>
     <row r="649" spans="1:3">
       <c r="A649" s="2">
-        <v>46329</v>
+        <v>46328</v>
       </c>
       <c r="B649">
         <v>1</v>
       </c>
       <c r="C649">
-        <v>491.59</v>
+        <v>491.88</v>
       </c>
     </row>
     <row r="650" spans="1:3">
       <c r="A650" s="2">
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="B650">
         <v>1</v>
       </c>
       <c r="C650">
-        <v>473.13</v>
+        <v>491.59</v>
       </c>
     </row>
     <row r="651" spans="1:3">
       <c r="A651" s="2">
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="B651">
         <v>1</v>
       </c>
       <c r="C651">
-        <v>461.26</v>
+        <v>473.13</v>
       </c>
     </row>
     <row r="652" spans="1:3">
       <c r="A652" s="2">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="B652">
         <v>1</v>
       </c>
       <c r="C652">
-        <v>488.59</v>
+        <v>461.26</v>
       </c>
     </row>
     <row r="653" spans="1:3">
       <c r="A653" s="2">
-        <v>46333</v>
+        <v>46332</v>
       </c>
       <c r="B653">
         <v>1</v>
       </c>
       <c r="C653">
-        <v>464.71</v>
+        <v>488.59</v>
       </c>
     </row>
     <row r="654" spans="1:3">
       <c r="A654" s="2">
-        <v>46334</v>
+        <v>46333</v>
       </c>
       <c r="B654">
         <v>1</v>
       </c>
       <c r="C654">
-        <v>466.08</v>
+        <v>464.71</v>
       </c>
     </row>
     <row r="655" spans="1:3">
       <c r="A655" s="2">
-        <v>46357</v>
+        <v>46334</v>
       </c>
       <c r="B655">
         <v>1</v>
       </c>
       <c r="C655">
-        <v>509.94</v>
+        <v>466.08</v>
       </c>
     </row>
     <row r="656" spans="1:3">
       <c r="A656" s="2">
-        <v>46358</v>
+        <v>46357</v>
       </c>
       <c r="B656">
         <v>1</v>
       </c>
       <c r="C656">
-        <v>490.58</v>
+        <v>509.94</v>
       </c>
     </row>
     <row r="657" spans="1:3">
       <c r="A657" s="2">
-        <v>46359</v>
+        <v>46358</v>
       </c>
       <c r="B657">
         <v>1</v>
       </c>
       <c r="C657">
-        <v>489.39</v>
+        <v>490.58</v>
       </c>
     </row>
     <row r="658" spans="1:3">
       <c r="A658" s="2">
-        <v>46360</v>
+        <v>46359</v>
       </c>
       <c r="B658">
         <v>1</v>
       </c>
       <c r="C658">
-        <v>473.13</v>
+        <v>489.39</v>
       </c>
     </row>
     <row r="659" spans="1:3">
       <c r="A659" s="2">
-        <v>46361</v>
+        <v>46360</v>
       </c>
       <c r="B659">
         <v>1</v>
       </c>
       <c r="C659">
-        <v>461.26</v>
+        <v>473.13</v>
       </c>
     </row>
     <row r="660" spans="1:3">
       <c r="A660" s="2">
-        <v>46362</v>
+        <v>46361</v>
       </c>
       <c r="B660">
         <v>1</v>
       </c>
       <c r="C660">
-        <v>487.76</v>
+        <v>461.26</v>
       </c>
     </row>
     <row r="661" spans="1:3">
       <c r="A661" s="2">
-        <v>46363</v>
+        <v>46362</v>
       </c>
       <c r="B661">
         <v>1</v>
       </c>
       <c r="C661">
-        <v>464.71</v>
+        <v>487.76</v>
       </c>
     </row>
     <row r="662" spans="1:3">
       <c r="A662" s="2">
+        <v>46363</v>
+      </c>
+      <c r="B662">
+        <v>1</v>
+      </c>
+      <c r="C662">
+        <v>464.71</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3">
+      <c r="A663" s="2">
         <v>46364</v>
       </c>
-      <c r="B662">
-        <v>1</v>
-      </c>
-      <c r="C662">
+      <c r="B663">
+        <v>1</v>
+      </c>
+      <c r="C663">
         <v>465.74</v>
       </c>
     </row>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1675"/>
+  <dimension ref="A1:C1676"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -18812,6 +18812,17 @@
         <v>458.45</v>
       </c>
     </row>
+    <row r="1676" spans="1:3">
+      <c r="A1676" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B1676">
+        <v>1</v>
+      </c>
+      <c r="C1676">
+        <v>455.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1676"/>
+  <dimension ref="A1:C1677"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -18823,6 +18823,17 @@
         <v>455.4</v>
       </c>
     </row>
+    <row r="1677" spans="1:3">
+      <c r="A1677" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B1677">
+        <v>1</v>
+      </c>
+      <c r="C1677">
+        <v>455.86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1677"/>
+  <dimension ref="A1:C1678"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -18834,6 +18834,17 @@
         <v>455.86</v>
       </c>
     </row>
+    <row r="1678" spans="1:3">
+      <c r="A1678" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B1678">
+        <v>1</v>
+      </c>
+      <c r="C1678">
+        <v>456.56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1678"/>
+  <dimension ref="A1:C1681"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -18845,6 +18845,39 @@
         <v>456.56</v>
       </c>
     </row>
+    <row r="1679" spans="1:3">
+      <c r="A1679" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B1679">
+        <v>1</v>
+      </c>
+      <c r="C1679">
+        <v>456.56</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:3">
+      <c r="A1680" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B1680">
+        <v>1</v>
+      </c>
+      <c r="C1680">
+        <v>456.56</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:3">
+      <c r="A1681" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B1681">
+        <v>1</v>
+      </c>
+      <c r="C1681">
+        <v>454.31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1681"/>
+  <dimension ref="A1:C1682"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -18878,6 +18878,17 @@
         <v>454.31</v>
       </c>
     </row>
+    <row r="1682" spans="1:3">
+      <c r="A1682" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B1682">
+        <v>1</v>
+      </c>
+      <c r="C1682">
+        <v>454.46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1682"/>
+  <dimension ref="A1:C1683"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -18889,6 +18889,17 @@
         <v>454.46</v>
       </c>
     </row>
+    <row r="1683" spans="1:3">
+      <c r="A1683" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B1683">
+        <v>1</v>
+      </c>
+      <c r="C1683">
+        <v>456.89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1683"/>
+  <dimension ref="A1:C1684"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -18900,6 +18900,17 @@
         <v>456.89</v>
       </c>
     </row>
+    <row r="1684" spans="1:3">
+      <c r="A1684" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B1684">
+        <v>1</v>
+      </c>
+      <c r="C1684">
+        <v>450.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1684"/>
+  <dimension ref="A1:C1685"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -18911,6 +18911,17 @@
         <v>450.79</v>
       </c>
     </row>
+    <row r="1685" spans="1:3">
+      <c r="A1685" s="2">
+        <v>46277</v>
+      </c>
+      <c r="B1685">
+        <v>1</v>
+      </c>
+      <c r="C1685">
+        <v>450.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
